--- a/BD.xlsx
+++ b/BD.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="25600" windowHeight="9880"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
   <si>
     <t>Имя файла</t>
   </si>
@@ -44,7 +44,16 @@
     <t>alpha_line</t>
   </si>
   <si>
-    <t>Массовый расход</t>
+    <t>rho_in</t>
+  </si>
+  <si>
+    <t>Vinf (R = 6)</t>
+  </si>
+  <si>
+    <t>Расход</t>
+  </si>
+  <si>
+    <t>Неустойчивость</t>
   </si>
   <si>
     <t>Комментарий</t>
@@ -56,9 +65,18 @@
     <t>0.44</t>
   </si>
   <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>нет</t>
+  </si>
+  <si>
     <t>0.45542</t>
   </si>
   <si>
+    <t>да</t>
+  </si>
+  <si>
     <t>0.266667</t>
   </si>
   <si>
@@ -69,6 +87,27 @@
   </si>
   <si>
     <t>0.06</t>
+  </si>
+  <si>
+    <t>≈2.5</t>
+  </si>
+  <si>
+    <t>0.08</t>
+  </si>
+  <si>
+    <t>0.55</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>≈8.3</t>
+  </si>
+  <si>
+    <t>нет (микро)</t>
+  </si>
+  <si>
+    <t>0.04</t>
   </si>
 </sst>
 </file>
@@ -81,7 +120,7 @@
     <numFmt numFmtId="176" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* &quot;-&quot;\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,6 +135,32 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF6F008A"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -577,141 +642,168 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1250,17 +1342,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.5" outlineLevelCol="6"/>
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="3" width="20.7818181818182" customWidth="1"/>
-    <col min="4" max="5" width="18.6636363636364" customWidth="1"/>
-    <col min="6" max="6" width="33.0636363636364" customWidth="1"/>
-    <col min="7" max="7" width="93.0727272727273" customWidth="1"/>
-    <col min="8" max="11" width="18.6636363636364" customWidth="1"/>
+    <col min="4" max="7" width="18.6636363636364" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="30.1454545454545" customWidth="1"/>
+    <col min="10" max="10" width="95.2454545454545" customWidth="1"/>
+    <col min="11" max="14" width="18.6636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" customHeight="1" spans="1:7">
+    <row r="1" ht="27" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1273,17 +1366,26 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" ht="27" customHeight="1" spans="1:7">
+    <row r="2" ht="27" customHeight="1" spans="1:10">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1294,157 +1396,253 @@
         <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="8"/>
     </row>
-    <row r="3" ht="27" customHeight="1" spans="1:7">
+    <row r="3" ht="27" customHeight="1" spans="1:10">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1">
         <v>0</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="8"/>
     </row>
-    <row r="4" ht="27" customHeight="1" spans="1:7">
+    <row r="4" ht="27" customHeight="1" spans="1:10">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" t="s">
+      <c r="E4" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="F4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="5" ht="27" customHeight="1" spans="1:7">
+    <row r="5" ht="27" customHeight="1" spans="1:10">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="1"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="8"/>
     </row>
-    <row r="6" ht="27" customHeight="1" spans="1:7">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+    <row r="6" ht="27" customHeight="1" spans="1:10">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="8"/>
     </row>
-    <row r="7" ht="27" customHeight="1" spans="1:7">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+    <row r="7" ht="27" customHeight="1" spans="1:10">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="8"/>
     </row>
-    <row r="8" ht="27" customHeight="1" spans="1:7">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+    <row r="8" ht="27" customHeight="1" spans="1:10">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
     </row>
-    <row r="9" ht="27" customHeight="1" spans="1:7">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+    <row r="9" ht="27" customHeight="1" spans="1:10">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
     </row>
-    <row r="10" ht="27" customHeight="1" spans="1:7">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+    <row r="10" ht="27" customHeight="1" spans="1:10">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
     </row>
-    <row r="11" ht="27" customHeight="1" spans="1:7">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+    <row r="11" ht="27" customHeight="1" spans="1:10">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
     </row>
-    <row r="12" ht="27" customHeight="1" spans="1:7">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+    <row r="12" ht="27" customHeight="1" spans="1:10">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
     </row>
-    <row r="13" ht="27" customHeight="1" spans="1:7">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+    <row r="13" ht="27" customHeight="1" spans="1:10">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
     </row>
-    <row r="14" ht="27" customHeight="1" spans="1:7">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+    <row r="14" ht="27" customHeight="1" spans="1:10">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
     </row>
-    <row r="15" ht="27" customHeight="1" spans="1:7">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+    <row r="15" ht="27" customHeight="1" spans="1:10">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
     </row>
-    <row r="16" ht="27" customHeight="1" spans="1:7">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+    <row r="16" ht="27" customHeight="1" spans="1:10">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
     </row>
     <row r="17" ht="27" customHeight="1"/>
     <row r="18" ht="27" customHeight="1"/>

--- a/BD.xlsx
+++ b/BD.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="9880"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="1" r:id="rId1"/>
@@ -26,12 +26,107 @@
 </workbook>
 </file>
 
+<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="ID_EC1D7148A9B44FF5B30FF6F13427E574"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14100810" y="3467100"/>
+          <a:ext cx="16725900" cy="9534525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="ID_E6919FB05A0C45D594936C73AB7E9DF8"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14100810" y="2946400"/>
+          <a:ext cx="16840200" cy="9791700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="ID_96DA28DADA944135B6EA5B59D14C9926"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14100810" y="2362200"/>
+          <a:ext cx="16811625" cy="9334500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+</etc:cellImages>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="63">
   <si>
     <t>Имя файла</t>
   </si>
   <si>
+    <t>Комп</t>
+  </si>
+  <si>
     <t>B0</t>
   </si>
   <si>
@@ -56,9 +151,18 @@
     <t>Неустойчивость</t>
   </si>
   <si>
+    <t>График r_pole</t>
+  </si>
+  <si>
+    <t>График phi_average</t>
+  </si>
+  <si>
     <t>Комментарий</t>
   </si>
   <si>
+    <t>Nuclon</t>
+  </si>
+  <si>
     <t>0.067358</t>
   </si>
   <si>
@@ -89,7 +193,10 @@
     <t>0.06</t>
   </si>
   <si>
-    <t>≈2.5</t>
+    <t>≈ 2.55</t>
+  </si>
+  <si>
+    <t>≈ 3.3</t>
   </si>
   <si>
     <t>0.08</t>
@@ -101,13 +208,106 @@
     <t>0.5</t>
   </si>
   <si>
-    <t>≈8.3</t>
-  </si>
-  <si>
-    <t>нет (микро)</t>
+    <t>≈ 2.41</t>
+  </si>
+  <si>
+    <t>≈ 8.35</t>
+  </si>
+  <si>
+    <t>нет (микро неустойчивость)</t>
   </si>
   <si>
     <t>0.04</t>
+  </si>
+  <si>
+    <t>≈ 3.47</t>
+  </si>
+  <si>
+    <t>≈ 2.7 (2 - 5)</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>≈ 2.65</t>
+  </si>
+  <si>
+    <t>≈ 2.2</t>
+  </si>
+  <si>
+    <t>HSE</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>≈ 1.8</t>
+  </si>
+  <si>
+    <t>≈ 4.67</t>
+  </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>≈ 2</t>
+  </si>
+  <si>
+    <t>≈ 4</t>
+  </si>
+  <si>
+    <t>Luna</t>
+  </si>
+  <si>
+    <t>0.11</t>
+  </si>
+  <si>
+    <t>≈ (1.5)</t>
+  </si>
+  <si>
+    <t>≈ (4.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≈ </t>
+  </si>
+  <si>
+    <t>≈</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>≈  (1.85)</t>
+  </si>
+  <si>
+    <t>≈  (7)</t>
+  </si>
+  <si>
+    <t>0.03</t>
+  </si>
+  <si>
+    <t>0.7</t>
+  </si>
+  <si>
+    <t>≈  (5)</t>
+  </si>
+  <si>
+    <t>≈  (3.7)</t>
+  </si>
+  <si>
+    <t>0.12</t>
+  </si>
+  <si>
+    <t>≈ (2.2)</t>
+  </si>
+  <si>
+    <t>≈ (4.48)</t>
+  </si>
+  <si>
+    <t>1.5</t>
   </si>
 </sst>
 </file>
@@ -120,7 +320,7 @@
     <numFmt numFmtId="176" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* &quot;-&quot;\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,8 +344,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF6F008A"/>
+      <b/>
+      <sz val="18"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -159,6 +359,20 @@
       <b/>
       <sz val="18"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -307,7 +521,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -316,6 +530,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -501,7 +727,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -522,6 +748,19 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -642,58 +881,52 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -705,109 +938,172 @@
     <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1342,314 +1638,586 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.5"/>
+  <dimension ref="A1:M22"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="3" width="20.7818181818182" customWidth="1"/>
-    <col min="4" max="7" width="18.6636363636364" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="30.1454545454545" customWidth="1"/>
-    <col min="10" max="10" width="95.2454545454545" customWidth="1"/>
-    <col min="11" max="14" width="18.6636363636364" customWidth="1"/>
+    <col min="1" max="1" width="11.6666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7777777777778" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.1111111111111" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.4444444444444" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.2222222222222" style="2" customWidth="1"/>
+    <col min="7" max="8" width="18.6666666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20" style="1" customWidth="1"/>
+    <col min="10" max="10" width="30.1481481481481" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.462962962963" style="1" customWidth="1"/>
+    <col min="12" max="12" width="25.1203703703704" style="1" customWidth="1"/>
+    <col min="13" max="13" width="95.25" style="1" customWidth="1"/>
+    <col min="14" max="17" width="18.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" customHeight="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="48" customHeight="1" spans="1:13">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" ht="27" customHeight="1" spans="1:10">
-      <c r="A2" s="1">
+    <row r="2" ht="46" customHeight="1" spans="1:13">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3">
         <v>0</v>
       </c>
-      <c r="C2" s="1">
+      <c r="D2" s="3">
         <v>0</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="10"/>
+    </row>
+    <row r="3" ht="46" customHeight="1" spans="1:13">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="10"/>
+    </row>
+    <row r="4" ht="46" customHeight="1" spans="1:13">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1" spans="1:13">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="9"/>
+      <c r="L5" s="11" t="str">
+        <f>_xlfn.DISPIMG("ID_96DA28DADA944135B6EA5B59D14C9926",1)</f>
+        <v>=DISPIMG("ID_96DA28DADA944135B6EA5B59D14C9926",1)</v>
+      </c>
+      <c r="M5" s="10"/>
+    </row>
+    <row r="6" ht="46" customHeight="1" spans="1:13">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="9"/>
+      <c r="L6" s="11" t="str">
+        <f>_xlfn.DISPIMG("ID_E6919FB05A0C45D594936C73AB7E9DF8",1)</f>
+        <v>=DISPIMG("ID_E6919FB05A0C45D594936C73AB7E9DF8",1)</v>
+      </c>
+      <c r="M6" s="10"/>
+    </row>
+    <row r="7" ht="46" customHeight="1" spans="1:13">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="9"/>
+      <c r="L7" s="11" t="str">
+        <f>_xlfn.DISPIMG("ID_EC1D7148A9B44FF5B30FF6F13427E574",1)</f>
+        <v>=DISPIMG("ID_EC1D7148A9B44FF5B30FF6F13427E574",1)</v>
+      </c>
+      <c r="M7" s="10"/>
+    </row>
+    <row r="8" ht="46" customHeight="1" spans="1:13">
+      <c r="A8" s="13">
+        <v>7</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="9"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="17"/>
+    </row>
+    <row r="9" ht="46" customHeight="1" spans="1:13">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="17"/>
+    </row>
+    <row r="10" ht="46" customHeight="1" spans="1:13">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="3"/>
+      <c r="L10" s="18"/>
+    </row>
+    <row r="11" ht="46" customHeight="1" spans="1:13">
+      <c r="A11" s="19">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="B11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="18"/>
+    </row>
+    <row r="12" ht="46" customHeight="1" spans="1:13">
+      <c r="A12" s="22"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="18"/>
+    </row>
+    <row r="13" ht="46" customHeight="1" spans="1:13">
+      <c r="A13" s="24">
         <v>12</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="7" t="s">
+      <c r="B13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="8"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="18"/>
     </row>
-    <row r="3" ht="27" customHeight="1" spans="1:10">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="14" ht="46" customHeight="1" spans="1:13">
+      <c r="A14" s="24">
+        <v>13</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="18"/>
+    </row>
+    <row r="15" ht="46" customHeight="1" spans="1:13">
+      <c r="A15" s="26">
         <v>14</v>
       </c>
-      <c r="C3" s="1">
-        <v>0</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="7" t="s">
+      <c r="B15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="18"/>
+    </row>
+    <row r="16" ht="46" customHeight="1" spans="1:13">
+      <c r="A16" s="22">
         <v>15</v>
       </c>
-      <c r="J3" s="8"/>
+      <c r="B16" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="18"/>
     </row>
-    <row r="4" ht="27" customHeight="1" spans="1:10">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>17</v>
-      </c>
+    <row r="17" ht="46" customHeight="1" spans="1:11">
+      <c r="A17" s="28"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
     </row>
-    <row r="5" ht="27" customHeight="1" spans="1:10">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="8"/>
+    <row r="18" ht="46" customHeight="1" spans="1:11">
+      <c r="A18" s="28"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
     </row>
-    <row r="6" ht="27" customHeight="1" spans="1:10">
-      <c r="A6" s="9">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" ht="27" customHeight="1" spans="1:10">
-      <c r="A7" s="9">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" ht="27" customHeight="1" spans="1:10">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-    </row>
-    <row r="9" ht="27" customHeight="1" spans="1:10">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-    </row>
-    <row r="10" ht="27" customHeight="1" spans="1:10">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-    </row>
-    <row r="11" ht="27" customHeight="1" spans="1:10">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-    </row>
-    <row r="12" ht="27" customHeight="1" spans="1:10">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-    </row>
-    <row r="13" ht="27" customHeight="1" spans="1:10">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-    </row>
-    <row r="14" ht="27" customHeight="1" spans="1:10">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-    </row>
-    <row r="15" ht="27" customHeight="1" spans="1:10">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-    </row>
-    <row r="16" ht="27" customHeight="1" spans="1:10">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-    </row>
-    <row r="17" ht="27" customHeight="1"/>
-    <row r="18" ht="27" customHeight="1"/>
-    <row r="19" ht="27" customHeight="1"/>
-    <row r="20" ht="27" customHeight="1"/>
-    <row r="21" ht="27" customHeight="1"/>
-    <row r="22" ht="27" customHeight="1"/>
+    <row r="19" ht="46" customHeight="1"/>
+    <row r="20" ht="46" customHeight="1"/>
+    <row r="21" ht="46" customHeight="1"/>
+    <row r="22" ht="46" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/BD.xlsx
+++ b/BD.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="75">
   <si>
     <t>Имя файла</t>
   </si>
@@ -268,7 +268,7 @@
     <t>≈ (1.5)</t>
   </si>
   <si>
-    <t>≈ (4.5)</t>
+    <t>≈ (5.5)</t>
   </si>
   <si>
     <t xml:space="preserve">≈ </t>
@@ -301,26 +301,63 @@
     <t>0.12</t>
   </si>
   <si>
+    <t>≈ (1.38)</t>
+  </si>
+  <si>
+    <t>≈ (4.2)</t>
+  </si>
+  <si>
+    <t>≈ (2.34)</t>
+  </si>
+  <si>
+    <t>≈ (2.1)</t>
+  </si>
+  <si>
+    <t>Неустойчивое странное решение. Видимо с такими параметрами нельзя посчитать</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>≈ (1.263)</t>
+  </si>
+  <si>
+    <t>≈ (6.7)</t>
+  </si>
+  <si>
+    <t>0.13</t>
+  </si>
+  <si>
+    <t>≈ (1.26)</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>0.6</t>
+  </si>
+  <si>
     <t>≈ (2.2)</t>
   </si>
   <si>
-    <t>≈ (4.48)</t>
-  </si>
-  <si>
-    <t>1.5</t>
+    <t>≈ (2.6)</t>
+  </si>
+  <si>
+    <t>Тут ветер сразу сверхзвуковой</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* &quot;-&quot;\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="mmm\.yy"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -371,6 +408,31 @@
     </font>
     <font>
       <b/>
+      <strike/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
@@ -521,7 +583,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -531,12 +593,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -881,137 +937,137 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1069,41 +1125,47 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1639,21 +1701,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.6666666666667" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7777777777778" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.2222222222222" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.1111111111111" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.4444444444444" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.2222222222222" style="2" customWidth="1"/>
-    <col min="7" max="8" width="18.6666666666667" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.6636363636364" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.2181818181818" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.1090909090909" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.4454545454545" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.2181818181818" style="2" customWidth="1"/>
+    <col min="7" max="8" width="18.6636363636364" style="1" customWidth="1"/>
     <col min="9" max="9" width="20" style="1" customWidth="1"/>
-    <col min="10" max="10" width="30.1481481481481" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.462962962963" style="1" customWidth="1"/>
-    <col min="12" max="12" width="25.1203703703704" style="1" customWidth="1"/>
-    <col min="13" max="13" width="95.25" style="1" customWidth="1"/>
-    <col min="14" max="17" width="18.6666666666667" customWidth="1"/>
+    <col min="10" max="10" width="30.1454545454545" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.4636363636364" style="1" customWidth="1"/>
+    <col min="12" max="12" width="25.1181818181818" style="1" customWidth="1"/>
+    <col min="13" max="13" width="95.2545454545455" style="1" customWidth="1"/>
+    <col min="14" max="17" width="18.6636363636364" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customHeight="1" spans="1:13">
@@ -2034,23 +2096,23 @@
       <c r="I11" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
       <c r="L11" s="18"/>
     </row>
     <row r="12" ht="46" customHeight="1" spans="1:13">
-      <c r="A12" s="22"/>
-      <c r="B12" s="21"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="5" t="s">
         <v>43</v>
       </c>
       <c r="G12" s="7" t="s">
@@ -2062,23 +2124,23 @@
       <c r="I12" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
       <c r="L12" s="18"/>
     </row>
     <row r="13" ht="46" customHeight="1" spans="1:13">
-      <c r="A13" s="24">
+      <c r="A13" s="21">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="25" t="s">
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="F13" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G13" s="7" t="s">
@@ -2090,23 +2152,23 @@
       <c r="I13" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
       <c r="L13" s="18"/>
     </row>
     <row r="14" ht="46" customHeight="1" spans="1:13">
-      <c r="A14" s="24">
+      <c r="A14" s="21">
         <v>13</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="25" t="s">
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F14" s="25" t="s">
+      <c r="F14" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G14" s="7" t="s">
@@ -2118,103 +2180,149 @@
       <c r="I14" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
       <c r="L14" s="18"/>
     </row>
     <row r="15" ht="46" customHeight="1" spans="1:13">
-      <c r="A15" s="26">
+      <c r="A15" s="22">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="25" t="s">
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="F15" s="4" t="s">
         <v>52</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
+        <v>61</v>
+      </c>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
       <c r="L15" s="18"/>
     </row>
     <row r="16" ht="46" customHeight="1" spans="1:13">
-      <c r="A16" s="22">
+      <c r="A16" s="23">
         <v>15</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="20" t="s">
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="26" t="s">
         <v>40</v>
       </c>
       <c r="G16" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="H16" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
+      <c r="H16" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="I16" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="J16" s="24"/>
+      <c r="K16" s="3"/>
       <c r="L16" s="18"/>
+      <c r="M16" s="1" t="s">
+        <v>64</v>
+      </c>
     </row>
-    <row r="17" ht="46" customHeight="1" spans="1:11">
-      <c r="A17" s="28"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
+    <row r="17" ht="46" customHeight="1" spans="1:13">
+      <c r="A17" s="29">
+        <v>16</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
       <c r="E17" s="20" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G17" s="29" t="s">
-        <v>62</v>
+        <v>52</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>65</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28"/>
+        <v>67</v>
+      </c>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
     </row>
-    <row r="18" ht="46" customHeight="1" spans="1:11">
-      <c r="A18" s="28"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28"/>
+    <row r="18" ht="46" customHeight="1" spans="1:13">
+      <c r="A18" s="29">
+        <v>17</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
     </row>
-    <row r="19" ht="46" customHeight="1"/>
+    <row r="19" ht="46" customHeight="1" spans="1:13">
+      <c r="A19" s="32">
+        <v>18</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
     <row r="20" ht="46" customHeight="1"/>
     <row r="21" ht="46" customHeight="1"/>
     <row r="22" ht="46" customHeight="1"/>

--- a/BD.xlsx
+++ b/BD.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="25600" windowHeight="9880"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="80">
   <si>
     <t>Имя файла</t>
   </si>
@@ -133,6 +133,9 @@
     <t>Vphi</t>
   </si>
   <si>
+    <t>F_grav</t>
+  </si>
+  <si>
     <t>F_line</t>
   </si>
   <si>
@@ -163,6 +166,9 @@
     <t>Nuclon</t>
   </si>
   <si>
+    <t>-0.187168</t>
+  </si>
+  <si>
     <t>0.067358</t>
   </si>
   <si>
@@ -331,6 +337,9 @@
     <t>≈ (1.26)</t>
   </si>
   <si>
+    <t>≈ (5)</t>
+  </si>
+  <si>
     <t>0.15</t>
   </si>
   <si>
@@ -344,6 +353,12 @@
   </si>
   <si>
     <t>Тут ветер сразу сверхзвуковой</t>
+  </si>
+  <si>
+    <t>-0.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -357,7 +372,7 @@
     <numFmt numFmtId="177" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* &quot;-&quot;\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="mmm\.yy"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -390,6 +405,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Cascadia Mono"/>
       <charset val="134"/>
     </font>
     <font>
@@ -937,133 +958,133 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1095,6 +1116,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1104,7 +1128,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1131,34 +1155,31 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1166,6 +1187,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1700,25 +1724,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.6636363636364" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.7818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.2181818181818" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.1090909090909" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.4454545454545" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.2181818181818" style="2" customWidth="1"/>
-    <col min="7" max="8" width="18.6636363636364" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20" style="1" customWidth="1"/>
-    <col min="10" max="10" width="30.1454545454545" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.4636363636364" style="1" customWidth="1"/>
-    <col min="12" max="12" width="25.1181818181818" style="1" customWidth="1"/>
-    <col min="13" max="13" width="95.2545454545455" style="1" customWidth="1"/>
-    <col min="14" max="17" width="18.6636363636364" customWidth="1"/>
+    <col min="4" max="5" width="17.1090909090909" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.4454545454545" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12.2181818181818" style="2" customWidth="1"/>
+    <col min="8" max="9" width="18.6636363636364" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20" style="1" customWidth="1"/>
+    <col min="11" max="11" width="30.1454545454545" style="1" customWidth="1"/>
+    <col min="12" max="12" width="18.4636363636364" style="1" customWidth="1"/>
+    <col min="13" max="13" width="25.1181818181818" style="1" customWidth="1"/>
+    <col min="14" max="14" width="95.2545454545455" style="1" customWidth="1"/>
+    <col min="15" max="18" width="18.6636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1" spans="1:13">
+    <row r="1" ht="48" customHeight="1" spans="1:14">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1731,16 +1755,16 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="7" t="s">
@@ -1755,16 +1779,19 @@
       <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="8" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" ht="46" customHeight="1" spans="1:13">
+    <row r="2" ht="46" customHeight="1" spans="1:14">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -1772,559 +1799,636 @@
       <c r="D2" s="3">
         <v>0</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="E2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="F2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9" t="s">
+      <c r="G2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
+      <c r="H2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="10"/>
       <c r="M2" s="10"/>
+      <c r="N2" s="11"/>
     </row>
-    <row r="3" ht="46" customHeight="1" spans="1:13">
+    <row r="3" ht="46" customHeight="1" spans="1:14">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="3">
         <v>0</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="F3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
+      <c r="G3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="10"/>
       <c r="M3" s="10"/>
+      <c r="N3" s="11"/>
     </row>
-    <row r="4" ht="46" customHeight="1" spans="1:13">
+    <row r="4" ht="46" customHeight="1" spans="1:14">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="10" t="s">
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10" t="s">
         <v>21</v>
       </c>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="11" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="5" ht="46" customHeight="1" spans="1:13">
+    <row r="5" ht="46" customHeight="1" spans="1:14">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>23</v>
+      <c r="E5" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="11" t="str">
+      <c r="G5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="10"/>
+      <c r="M5" s="12" t="str">
         <f>_xlfn.DISPIMG("ID_96DA28DADA944135B6EA5B59D14C9926",1)</f>
         <v>=DISPIMG("ID_96DA28DADA944135B6EA5B59D14C9926",1)</v>
       </c>
-      <c r="M5" s="10"/>
+      <c r="N5" s="11"/>
     </row>
-    <row r="6" ht="46" customHeight="1" spans="1:13">
+    <row r="6" ht="46" customHeight="1" spans="1:14">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="7" t="s">
+      <c r="E6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="G6" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="H6" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="I6" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="K6" s="9"/>
-      <c r="L6" s="11" t="str">
+      <c r="J6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="10"/>
+      <c r="M6" s="12" t="str">
         <f>_xlfn.DISPIMG("ID_E6919FB05A0C45D594936C73AB7E9DF8",1)</f>
         <v>=DISPIMG("ID_E6919FB05A0C45D594936C73AB7E9DF8",1)</v>
       </c>
-      <c r="M6" s="10"/>
+      <c r="N6" s="11"/>
     </row>
-    <row r="7" ht="46" customHeight="1" spans="1:13">
+    <row r="7" ht="46" customHeight="1" spans="1:14">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>32</v>
+      <c r="E7" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="11" t="str">
+      <c r="G7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="10"/>
+      <c r="M7" s="12" t="str">
         <f>_xlfn.DISPIMG("ID_EC1D7148A9B44FF5B30FF6F13427E574",1)</f>
         <v>=DISPIMG("ID_EC1D7148A9B44FF5B30FF6F13427E574",1)</v>
       </c>
-      <c r="M7" s="10"/>
+      <c r="N7" s="11"/>
     </row>
-    <row r="8" ht="46" customHeight="1" spans="1:13">
-      <c r="A8" s="13">
+    <row r="8" ht="46" customHeight="1" spans="1:14">
+      <c r="A8" s="14">
         <v>7</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="13" t="s">
+      <c r="B8" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>35</v>
+      <c r="E8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="10"/>
       <c r="L8" s="3"/>
-      <c r="M8" s="17"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="18"/>
     </row>
-    <row r="9" ht="46" customHeight="1" spans="1:13">
+    <row r="9" ht="46" customHeight="1" spans="1:14">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>39</v>
+      <c r="E9" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="G9" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="J9" s="3"/>
+      <c r="H9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>44</v>
+      </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
-      <c r="M9" s="17"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="18"/>
     </row>
-    <row r="10" ht="46" customHeight="1" spans="1:13">
+    <row r="10" ht="46" customHeight="1" spans="1:14">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>39</v>
+      <c r="E10" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="I10" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="J10" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="18"/>
+      <c r="H10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="3"/>
+      <c r="M10" s="19"/>
     </row>
-    <row r="11" ht="46" customHeight="1" spans="1:13">
-      <c r="A11" s="19">
+    <row r="11" ht="46" customHeight="1" spans="1:14">
+      <c r="A11" s="20">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="I11" s="9" t="s">
+      <c r="E11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="J11" s="3"/>
+      <c r="G11" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="K11" s="3"/>
-      <c r="L11" s="18"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="19"/>
     </row>
-    <row r="12" ht="46" customHeight="1" spans="1:13">
-      <c r="A12" s="21"/>
+    <row r="12" ht="46" customHeight="1" spans="1:14">
+      <c r="A12" s="20"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>32</v>
+      <c r="E12" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="J12" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>53</v>
+      </c>
       <c r="K12" s="3"/>
-      <c r="L12" s="18"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="19"/>
     </row>
-    <row r="13" ht="46" customHeight="1" spans="1:13">
-      <c r="A13" s="21">
+    <row r="13" ht="46" customHeight="1" spans="1:14">
+      <c r="A13" s="20">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
-      <c r="E13" s="4" t="s">
-        <v>52</v>
+      <c r="E13" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I13" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="J13" s="3"/>
+      <c r="G13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="K13" s="3"/>
-      <c r="L13" s="18"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="19"/>
     </row>
-    <row r="14" ht="46" customHeight="1" spans="1:13">
-      <c r="A14" s="21">
+    <row r="14" ht="46" customHeight="1" spans="1:14">
+      <c r="A14" s="20">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
-      <c r="E14" s="4" t="s">
-        <v>55</v>
+      <c r="E14" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="G14" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="J14" s="3"/>
+      <c r="H14" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>60</v>
+      </c>
       <c r="K14" s="3"/>
-      <c r="L14" s="18"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="19"/>
     </row>
-    <row r="15" ht="46" customHeight="1" spans="1:13">
+    <row r="15" ht="46" customHeight="1" spans="1:14">
       <c r="A15" s="22">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
-      <c r="E15" s="4" t="s">
-        <v>59</v>
+      <c r="E15" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I15" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="3"/>
+      <c r="G15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>63</v>
+      </c>
       <c r="K15" s="3"/>
-      <c r="L15" s="18"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="19"/>
     </row>
-    <row r="16" ht="46" customHeight="1" spans="1:13">
+    <row r="16" ht="46" customHeight="1" spans="1:14">
       <c r="A16" s="23">
         <v>15</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C16" s="24"/>
       <c r="D16" s="24"/>
-      <c r="E16" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="G16" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="H16" s="28" t="s">
-        <v>62</v>
+      <c r="E16" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" s="27" t="s">
+        <v>54</v>
       </c>
       <c r="I16" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="J16" s="24"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="J16" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="K16" s="24"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="1" t="s">
+        <v>66</v>
+      </c>
     </row>
-    <row r="17" ht="46" customHeight="1" spans="1:13">
+    <row r="17" ht="46" customHeight="1" spans="1:14">
       <c r="A17" s="29">
         <v>16</v>
       </c>
-      <c r="B17" s="21" t="s">
-        <v>13</v>
+      <c r="B17" s="20" t="s">
+        <v>14</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
-      <c r="E17" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G17" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I17" s="9" t="s">
+      <c r="E17" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
+      <c r="I17" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
     </row>
-    <row r="18" ht="46" customHeight="1" spans="1:13">
+    <row r="18" ht="46" customHeight="1" spans="1:14">
       <c r="A18" s="29">
         <v>17</v>
       </c>
-      <c r="B18" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="4" t="s">
-        <v>68</v>
+      <c r="B18" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
+      <c r="H18" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
     </row>
-    <row r="19" ht="46" customHeight="1" spans="1:13">
+    <row r="19" ht="46" customHeight="1" spans="1:14">
       <c r="A19" s="32">
         <v>18</v>
       </c>
-      <c r="B19" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>70</v>
+      <c r="B19" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1" spans="1:14">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H19" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>74</v>
+      <c r="G20" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="20" ht="46" customHeight="1"/>
-    <row r="21" ht="46" customHeight="1"/>
+    <row r="21" ht="46" customHeight="1" spans="1:14">
+      <c r="E21" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
     <row r="22" ht="46" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BD.xlsx
+++ b/BD.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="9880"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="1" r:id="rId1"/>
@@ -119,11 +119,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="98">
   <si>
     <t>Имя файла</t>
   </si>
   <si>
+    <t>Предшественник</t>
+  </si>
+  <si>
     <t>Комп</t>
   </si>
   <si>
@@ -136,6 +139,9 @@
     <t>F_grav</t>
   </si>
   <si>
+    <t>const_p</t>
+  </si>
+  <si>
     <t>F_line</t>
   </si>
   <si>
@@ -151,6 +157,9 @@
     <t>Расход</t>
   </si>
   <si>
+    <t>Дозвук ли по Vr вблизи границы</t>
+  </si>
+  <si>
     <t>Неустойчивость</t>
   </si>
   <si>
@@ -169,6 +178,9 @@
     <t>-0.187168</t>
   </si>
   <si>
+    <t>0.000186401</t>
+  </si>
+  <si>
     <t>0.067358</t>
   </si>
   <si>
@@ -178,13 +190,16 @@
     <t>0.45</t>
   </si>
   <si>
+    <t>да</t>
+  </si>
+  <si>
     <t>нет</t>
   </si>
   <si>
     <t>0.45542</t>
   </si>
   <si>
-    <t>да</t>
+    <t>да (микро на экваторе)</t>
   </si>
   <si>
     <t>0.266667</t>
@@ -241,6 +256,9 @@
     <t>≈ 2.2</t>
   </si>
   <si>
+    <t>почти (бывает сверхзвук вблизи границы на средних широтах)</t>
+  </si>
+  <si>
     <t>HSE</t>
   </si>
   <si>
@@ -256,6 +274,9 @@
     <t>≈ 4.67</t>
   </si>
   <si>
+    <t>нет (вблизи экватора есть сверхзвуковые зоны)</t>
+  </si>
+  <si>
     <t>0.2</t>
   </si>
   <si>
@@ -277,6 +298,9 @@
     <t>≈ (5.5)</t>
   </si>
   <si>
+    <t>нет (на средних широтах сверхзвук)</t>
+  </si>
+  <si>
     <t xml:space="preserve">≈ </t>
   </si>
   <si>
@@ -358,7 +382,37 @@
     <t>-0.22</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>≈ (2.68)</t>
+  </si>
+  <si>
+    <t>≈ (7)</t>
+  </si>
+  <si>
+    <t>-0.13</t>
+  </si>
+  <si>
+    <t>0.00015</t>
+  </si>
+  <si>
+    <t>≈ (6)</t>
+  </si>
+  <si>
+    <t>0.0003</t>
+  </si>
+  <si>
+    <t>≈ (1.11)</t>
+  </si>
+  <si>
+    <t>≈ (4)</t>
+  </si>
+  <si>
+    <t>0.0005</t>
+  </si>
+  <si>
+    <t>≈ (0.94)</t>
+  </si>
+  <si>
+    <t>0.0006</t>
   </si>
 </sst>
 </file>
@@ -372,9 +426,16 @@
     <numFmt numFmtId="177" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* &quot;-&quot;\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="mmm\.yy"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="35">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -390,6 +451,14 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -398,6 +467,13 @@
     <font>
       <b/>
       <sz val="18"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -454,6 +530,14 @@
     </font>
     <font>
       <b/>
+      <strike/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
@@ -604,7 +688,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -614,6 +698,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -958,137 +1054,137 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1098,97 +1194,127 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1724,44 +1850,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.5"/>
+  <dimension ref="A1:Q53"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.6636363636364" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7818181818182" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.2181818181818" style="1" customWidth="1"/>
-    <col min="4" max="5" width="17.1090909090909" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.4454545454545" style="2" customWidth="1"/>
-    <col min="7" max="7" width="12.2181818181818" style="2" customWidth="1"/>
-    <col min="8" max="9" width="18.6636363636364" style="1" customWidth="1"/>
-    <col min="10" max="10" width="20" style="1" customWidth="1"/>
-    <col min="11" max="11" width="30.1454545454545" style="1" customWidth="1"/>
-    <col min="12" max="12" width="18.4636363636364" style="1" customWidth="1"/>
-    <col min="13" max="13" width="25.1181818181818" style="1" customWidth="1"/>
-    <col min="14" max="14" width="95.2545454545455" style="1" customWidth="1"/>
-    <col min="15" max="18" width="18.6636363636364" customWidth="1"/>
+    <col min="1" max="1" width="11.6666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.55555555555556" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7777777777778" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.2222222222222" style="1" customWidth="1"/>
+    <col min="5" max="7" width="17.1111111111111" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.4444444444444" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.2222222222222" style="2" customWidth="1"/>
+    <col min="10" max="11" width="18.6666666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="20" style="1" customWidth="1"/>
+    <col min="13" max="13" width="48.4444444444444" style="3" customWidth="1"/>
+    <col min="14" max="14" width="30.1481481481481" style="1" customWidth="1"/>
+    <col min="15" max="15" width="18.462962962963" style="1" customWidth="1"/>
+    <col min="16" max="16" width="25.1203703703704" style="1" customWidth="1"/>
+    <col min="17" max="17" width="95.25" style="1" customWidth="1"/>
+    <col min="18" max="21" width="18.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1" spans="1:14">
-      <c r="A1" s="3" t="s">
+    <row r="1" ht="48" customHeight="1" spans="1:17">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="6" t="s">
@@ -1770,666 +1898,951 @@
       <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="9" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" ht="46" customHeight="1" spans="1:14">
-      <c r="A2" s="3">
+    <row r="2" ht="46" customHeight="1" spans="1:17">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="3">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="4">
         <v>0</v>
       </c>
-      <c r="D2" s="3">
+      <c r="E2" s="4">
         <v>0</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="F2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="15"/>
+    </row>
+    <row r="3" ht="46" customHeight="1" spans="1:17">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="D3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10" t="s">
+      <c r="G3" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="11"/>
+      <c r="H3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="15"/>
     </row>
-    <row r="3" ht="46" customHeight="1" spans="1:14">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="3" t="s">
+    <row r="4" ht="46" customHeight="1" spans="1:17">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="3">
-        <v>0</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="5" t="s">
+      <c r="I4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1" spans="1:17">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="D5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10" t="s">
+      <c r="G5" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="11"/>
-    </row>
-    <row r="4" ht="46" customHeight="1" spans="1:14">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="J5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="11" t="s">
+      <c r="K5" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="13" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" ht="46" customHeight="1" spans="1:14">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="10"/>
-      <c r="M5" s="12" t="str">
+      <c r="O5" s="13"/>
+      <c r="P5" s="16" t="str">
         <f>_xlfn.DISPIMG("ID_96DA28DADA944135B6EA5B59D14C9926",1)</f>
         <v>=DISPIMG("ID_96DA28DADA944135B6EA5B59D14C9926",1)</v>
       </c>
-      <c r="N5" s="11"/>
+      <c r="Q5" s="15"/>
     </row>
-    <row r="6" ht="46" customHeight="1" spans="1:14">
-      <c r="A6" s="3">
+    <row r="6" ht="46" customHeight="1" spans="1:17">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="13" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" s="10" t="s">
+      <c r="E6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="L6" s="10"/>
-      <c r="M6" s="12" t="str">
+      <c r="I6" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6" s="14"/>
+      <c r="N6" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="O6" s="13"/>
+      <c r="P6" s="16" t="str">
         <f>_xlfn.DISPIMG("ID_E6919FB05A0C45D594936C73AB7E9DF8",1)</f>
         <v>=DISPIMG("ID_E6919FB05A0C45D594936C73AB7E9DF8",1)</v>
       </c>
-      <c r="N6" s="11"/>
+      <c r="Q6" s="15"/>
     </row>
-    <row r="7" ht="46" customHeight="1" spans="1:14">
-      <c r="A7" s="3">
+    <row r="7" ht="46" customHeight="1" spans="1:17">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="10" t="s">
+      <c r="J7" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="J7" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="10"/>
-      <c r="M7" s="12" t="str">
+      <c r="K7" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7" s="14"/>
+      <c r="N7" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" s="13"/>
+      <c r="P7" s="16" t="str">
         <f>_xlfn.DISPIMG("ID_EC1D7148A9B44FF5B30FF6F13427E574",1)</f>
         <v>=DISPIMG("ID_EC1D7148A9B44FF5B30FF6F13427E574",1)</v>
       </c>
-      <c r="N7" s="11"/>
+      <c r="Q7" s="15"/>
     </row>
-    <row r="8" ht="46" customHeight="1" spans="1:14">
-      <c r="A8" s="14">
+    <row r="8" ht="46" customHeight="1" spans="1:17">
+      <c r="A8" s="18">
         <v>7</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="18"/>
+      <c r="C8" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="N8" s="13"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="23"/>
+    </row>
+    <row r="9" ht="46" customHeight="1" spans="1:17">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="23"/>
+    </row>
+    <row r="10" ht="46" customHeight="1" spans="1:17">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10" s="14"/>
+      <c r="N10" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="O10" s="4"/>
+      <c r="P10" s="24"/>
+    </row>
+    <row r="11" ht="46" customHeight="1" spans="1:17">
+      <c r="A11" s="25">
+        <v>10</v>
+      </c>
+      <c r="B11" s="25"/>
+      <c r="C11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="24"/>
+    </row>
+    <row r="12" ht="46" customHeight="1" spans="1:17">
+      <c r="A12" s="25"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="M12" s="14"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="24"/>
+    </row>
+    <row r="13" ht="46" customHeight="1" spans="1:17">
+      <c r="A13" s="25">
+        <v>12</v>
+      </c>
+      <c r="B13" s="25"/>
+      <c r="C13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="M13" s="14"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="24"/>
+    </row>
+    <row r="14" ht="46" customHeight="1" spans="1:17">
+      <c r="A14" s="25">
+        <v>13</v>
+      </c>
+      <c r="B14" s="25"/>
+      <c r="C14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="M14" s="14"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="24"/>
+    </row>
+    <row r="15" ht="46" customHeight="1" spans="1:17">
+      <c r="A15" s="27">
         <v>14</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="9" t="s">
+      <c r="B15" s="27"/>
+      <c r="C15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="M15" s="14"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="24"/>
+    </row>
+    <row r="16" ht="46" customHeight="1" spans="1:17">
+      <c r="A16" s="28">
         <v>15</v>
       </c>
-      <c r="F8" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="18"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="J16" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="K16" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="L16" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="M16" s="34"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
-    <row r="9" ht="46" customHeight="1" spans="1:14">
-      <c r="A9" s="3">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="18"/>
+    <row r="17" ht="46" customHeight="1" spans="1:17">
+      <c r="A17" s="35">
+        <v>16</v>
+      </c>
+      <c r="B17" s="36"/>
+      <c r="C17" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J17" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="M17" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
     </row>
-    <row r="10" ht="46" customHeight="1" spans="1:14">
-      <c r="A10" s="3">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" s="3"/>
-      <c r="M10" s="19"/>
+    <row r="18" ht="46" customHeight="1" spans="1:17">
+      <c r="A18" s="35">
+        <v>17</v>
+      </c>
+      <c r="B18" s="36"/>
+      <c r="C18" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K18" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="M18" s="10"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
     </row>
-    <row r="11" ht="46" customHeight="1" spans="1:14">
-      <c r="A11" s="20">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="19"/>
+    <row r="19" ht="46" customHeight="1" spans="1:17">
+      <c r="A19" s="39">
+        <v>18</v>
+      </c>
+      <c r="B19" s="39"/>
+      <c r="C19" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K19" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="M19" s="40"/>
+      <c r="Q19" s="1" t="s">
+        <v>85</v>
+      </c>
     </row>
-    <row r="12" ht="46" customHeight="1" spans="1:14">
-      <c r="A12" s="20"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="19"/>
-    </row>
-    <row r="13" ht="46" customHeight="1" spans="1:14">
-      <c r="A13" s="20">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="19"/>
-    </row>
-    <row r="14" ht="46" customHeight="1" spans="1:14">
-      <c r="A14" s="20">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="19"/>
-    </row>
-    <row r="15" ht="46" customHeight="1" spans="1:14">
-      <c r="A15" s="22">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="19"/>
-    </row>
-    <row r="16" ht="46" customHeight="1" spans="1:14">
-      <c r="A16" s="23">
-        <v>15</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="G16" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="I16" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="J16" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="K16" s="24"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" ht="46" customHeight="1" spans="1:14">
-      <c r="A17" s="29">
-        <v>16</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H17" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-    </row>
-    <row r="18" ht="46" customHeight="1" spans="1:14">
-      <c r="A18" s="29">
-        <v>17</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-    </row>
-    <row r="19" ht="46" customHeight="1" spans="1:14">
-      <c r="A19" s="32">
-        <v>18</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" ht="46" customHeight="1" spans="1:14">
+    <row r="20" ht="46" customHeight="1" spans="1:17">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="33" t="s">
+      <c r="C20" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="43" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="L20" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="M20" s="41"/>
+    </row>
+    <row r="21" ht="46" customHeight="1" spans="1:17">
+      <c r="A21" s="25"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="H21" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="M21" s="41"/>
+    </row>
+    <row r="22" ht="46" customHeight="1" spans="1:17">
+      <c r="A22" s="42">
+        <v>21</v>
+      </c>
+      <c r="B22" s="36">
+        <v>17</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F20" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>30</v>
+      <c r="I22" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="21" ht="46" customHeight="1" spans="1:14">
-      <c r="E21" s="1" t="s">
-        <v>79</v>
+    <row r="23" ht="46" customHeight="1" spans="1:17">
+      <c r="A23" s="42">
+        <v>22</v>
+      </c>
+      <c r="B23" s="36">
+        <v>21</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="22" ht="46" customHeight="1"/>
+    <row r="24" ht="46" customHeight="1" spans="1:17">
+      <c r="A24" s="42">
+        <v>23</v>
+      </c>
+      <c r="B24" s="36">
+        <v>21</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" ht="46" customHeight="1"/>
+    <row r="26" ht="46" customHeight="1"/>
+    <row r="27" ht="46" customHeight="1"/>
+    <row r="28" ht="46" customHeight="1"/>
+    <row r="29" ht="46" customHeight="1"/>
+    <row r="30" ht="46" customHeight="1"/>
+    <row r="31" ht="46" customHeight="1"/>
+    <row r="32" ht="46" customHeight="1"/>
+    <row r="33" ht="46" customHeight="1"/>
+    <row r="34" ht="46" customHeight="1"/>
+    <row r="35" ht="46" customHeight="1"/>
+    <row r="36" ht="46" customHeight="1"/>
+    <row r="37" ht="46" customHeight="1"/>
+    <row r="38" ht="46" customHeight="1"/>
+    <row r="39" ht="46" customHeight="1"/>
+    <row r="40" ht="46" customHeight="1"/>
+    <row r="41" ht="46" customHeight="1"/>
+    <row r="42" ht="46" customHeight="1"/>
+    <row r="43" ht="46" customHeight="1"/>
+    <row r="44" ht="46" customHeight="1"/>
+    <row r="45" ht="46" customHeight="1"/>
+    <row r="46" ht="46" customHeight="1"/>
+    <row r="47" ht="46" customHeight="1"/>
+    <row r="48" ht="46" customHeight="1"/>
+    <row r="49" ht="46" customHeight="1"/>
+    <row r="50" ht="46" customHeight="1"/>
+    <row r="51" ht="46" customHeight="1"/>
+    <row r="52" ht="46" customHeight="1"/>
+    <row r="53" ht="46" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/BD.xlsx
+++ b/BD.xlsx
@@ -715,6 +715,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -872,12 +878,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1060,7 +1060,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1084,16 +1084,16 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1102,78 +1102,78 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1184,7 +1184,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1312,6 +1312,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1">
@@ -2654,7 +2657,7 @@
       <c r="C20" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="F20" s="43" t="s">
+      <c r="F20" s="44" t="s">
         <v>86</v>
       </c>
       <c r="G20" s="12" t="s">
@@ -2689,7 +2692,7 @@
       <c r="E21" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F21" s="43" t="s">
+      <c r="F21" s="44" t="s">
         <v>89</v>
       </c>
       <c r="G21" s="12" t="s">
@@ -2781,7 +2784,7 @@
       </c>
     </row>
     <row r="24" ht="46" customHeight="1" spans="1:17">
-      <c r="A24" s="42">
+      <c r="A24" s="43">
         <v>23</v>
       </c>
       <c r="B24" s="36">
